--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{864B0FD9-0AFC-4C57-A4C8-84038A85916D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8907D49D-82AF-4DD6-8AEE-041DA0A770C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1241"/>
+  <dimension ref="A1:I1242"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40091,6 +40091,35 @@
       </c>
       <c r="I1241">
         <v>27</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1242">
+        <v>1241</v>
+      </c>
+      <c r="B1242">
+        <v>20260912</v>
+      </c>
+      <c r="C1242">
+        <v>7</v>
+      </c>
+      <c r="D1242">
+        <v>13</v>
+      </c>
+      <c r="E1242">
+        <v>16</v>
+      </c>
+      <c r="F1242">
+        <v>23</v>
+      </c>
+      <c r="G1242">
+        <v>24</v>
+      </c>
+      <c r="H1242">
+        <v>43</v>
+      </c>
+      <c r="I1242">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8907D49D-82AF-4DD6-8AEE-041DA0A770C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF929E-2275-48CA-A972-284D6A3C8099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41865" yWindow="2190" windowWidth="32880" windowHeight="17115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1242"/>
+  <dimension ref="A1:I1243"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40119,6 +40119,35 @@
         <v>43</v>
       </c>
       <c r="I1242">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1243">
+        <v>1242</v>
+      </c>
+      <c r="B1243">
+        <v>20260919</v>
+      </c>
+      <c r="C1243">
+        <v>2</v>
+      </c>
+      <c r="D1243">
+        <v>4</v>
+      </c>
+      <c r="E1243">
+        <v>10</v>
+      </c>
+      <c r="F1243">
+        <v>16</v>
+      </c>
+      <c r="G1243">
+        <v>31</v>
+      </c>
+      <c r="H1243">
+        <v>41</v>
+      </c>
+      <c r="I1243">
         <v>9</v>
       </c>
     </row>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFF929E-2275-48CA-A972-284D6A3C8099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78EF709-FB7B-4B2F-92EF-70FF97014EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41865" yWindow="2190" windowWidth="32880" windowHeight="17115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61305" yWindow="675" windowWidth="24480" windowHeight="18990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1243"/>
+  <dimension ref="A1:I1244"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40149,6 +40149,35 @@
       </c>
       <c r="I1243">
         <v>9</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1244">
+        <v>1243</v>
+      </c>
+      <c r="B1244">
+        <v>20260926</v>
+      </c>
+      <c r="C1244">
+        <v>9</v>
+      </c>
+      <c r="D1244">
+        <v>18</v>
+      </c>
+      <c r="E1244">
+        <v>24</v>
+      </c>
+      <c r="F1244">
+        <v>38</v>
+      </c>
+      <c r="G1244">
+        <v>43</v>
+      </c>
+      <c r="H1244">
+        <v>44</v>
+      </c>
+      <c r="I1244">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78EF709-FB7B-4B2F-92EF-70FF97014EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD24873-2FE6-4696-B857-F4C1897115E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61305" yWindow="675" windowWidth="24480" windowHeight="18990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38655" yWindow="1410" windowWidth="26340" windowHeight="18105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1244"/>
+  <dimension ref="A1:I1245"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40178,6 +40178,35 @@
       </c>
       <c r="I1244">
         <v>35</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1245">
+        <v>1244</v>
+      </c>
+      <c r="B1245">
+        <v>20261003</v>
+      </c>
+      <c r="C1245">
+        <v>1</v>
+      </c>
+      <c r="D1245">
+        <v>13</v>
+      </c>
+      <c r="E1245">
+        <v>18</v>
+      </c>
+      <c r="F1245">
+        <v>26</v>
+      </c>
+      <c r="G1245">
+        <v>34</v>
+      </c>
+      <c r="H1245">
+        <v>38</v>
+      </c>
+      <c r="I1245">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD24873-2FE6-4696-B857-F4C1897115E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C656EEE-0DC9-431A-897E-51F8B34E06E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38655" yWindow="1410" windowWidth="26340" windowHeight="18105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39810" yWindow="960" windowWidth="22515" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1245"/>
+  <dimension ref="A1:I1246"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40207,6 +40207,35 @@
       </c>
       <c r="I1245">
         <v>25</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1246">
+        <v>1245</v>
+      </c>
+      <c r="B1246">
+        <v>20261010</v>
+      </c>
+      <c r="C1246">
+        <v>4</v>
+      </c>
+      <c r="D1246">
+        <v>5</v>
+      </c>
+      <c r="E1246">
+        <v>25</v>
+      </c>
+      <c r="F1246">
+        <v>28</v>
+      </c>
+      <c r="G1246">
+        <v>32</v>
+      </c>
+      <c r="H1246">
+        <v>42</v>
+      </c>
+      <c r="I1246">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C656EEE-0DC9-431A-897E-51F8B34E06E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC9D88F-A290-4B42-BC0B-3705759D4EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39810" yWindow="960" windowWidth="22515" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41280" yWindow="1905" windowWidth="19005" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1246"/>
+  <dimension ref="A1:I1247"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40236,6 +40236,35 @@
       </c>
       <c r="I1246">
         <v>12</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1247">
+        <v>1246</v>
+      </c>
+      <c r="B1247">
+        <v>20261017</v>
+      </c>
+      <c r="C1247">
+        <v>16</v>
+      </c>
+      <c r="D1247">
+        <v>22</v>
+      </c>
+      <c r="E1247">
+        <v>23</v>
+      </c>
+      <c r="F1247">
+        <v>24</v>
+      </c>
+      <c r="G1247">
+        <v>27</v>
+      </c>
+      <c r="H1247">
+        <v>28</v>
+      </c>
+      <c r="I1247">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/lotto_history.xlsx
+++ b/data/lotto_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLottoAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC9D88F-A290-4B42-BC0B-3705759D4EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBBFCF5-9400-4B74-AF60-B053DC1763D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41280" yWindow="1905" windowWidth="19005" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1247"/>
+  <dimension ref="A1:I1248"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -40265,6 +40265,35 @@
       </c>
       <c r="I1247">
         <v>6</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1248">
+        <v>1247</v>
+      </c>
+      <c r="B1248">
+        <v>20261024</v>
+      </c>
+      <c r="C1248">
+        <v>8</v>
+      </c>
+      <c r="D1248">
+        <v>14</v>
+      </c>
+      <c r="E1248">
+        <v>21</v>
+      </c>
+      <c r="F1248">
+        <v>22</v>
+      </c>
+      <c r="G1248">
+        <v>42</v>
+      </c>
+      <c r="H1248">
+        <v>45</v>
+      </c>
+      <c r="I1248">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
